--- a/data/再保偿付能力2025Q1-0901.xlsx
+++ b/data/再保偿付能力2025Q1-0901.xlsx
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.2487</v>
+        <v>3.248671</v>
       </c>
       <c r="D18" t="n">
-        <v>3.2487</v>
+        <v>3.248671</v>
       </c>
       <c r="E18" t="n">
         <v>6574862</v>

--- a/data/再保偿付能力2025Q1-0901.xlsx
+++ b/data/再保偿付能力2025Q1-0901.xlsx
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.248671</v>
+        <v>3.2487</v>
       </c>
       <c r="D18" t="n">
-        <v>3.248671</v>
+        <v>3.2487</v>
       </c>
       <c r="E18" t="n">
         <v>6574862</v>
